--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513651_FASEFINALAFFA1_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513651_FASEFINALAFFA1_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7818</v>
+        <v>1.5176</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0527</v>
+        <v>1.18</v>
       </c>
       <c r="F2" t="n">
-        <v>1.729</v>
+        <v>0.3376</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.1317</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6266</v>
+        <v>-0.621</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6353</v>
+        <v>0.4893</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0455</v>
+        <v>0.3458</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6029</v>
+        <v>0.1026</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6484</v>
+        <v>0.2432</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0368</v>
+        <v>-0.4775</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0236</v>
+        <v>-0.7236</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0131</v>
+        <v>0.2461</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1947</v>
+        <v>-0.9737</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7789</v>
+        <v>1.3632</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2473</v>
+        <v>0.0388</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0775</v>
+        <v>0.3073</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3248</v>
+        <v>-0.2686</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9416</v>
+        <v>1.2211</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2795</v>
+        <v>1.5005</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6621</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9566</v>
+        <v>1.4549</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3964</v>
+        <v>-0.2463</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5602</v>
+        <v>1.7012</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1317</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.621</v>
+        <v>-0.6266</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4893</v>
+        <v>0.6353</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3458</v>
+        <v>0.0455</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1026</v>
+        <v>-0.6029</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2432</v>
+        <v>0.6484</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4775</v>
+        <v>-0.0368</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7236</v>
+        <v>-0.0236</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2461</v>
+        <v>-0.0131</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3895</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9737</v>
+        <v>-0.1947</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3632</v>
+        <v>0.7789</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5222</v>
+        <v>-0.0796</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4762</v>
+        <v>-0.3765</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.046</v>
+        <v>0.2969</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2211</v>
+        <v>0.9416</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5005</v>
+        <v>0.2795</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2795</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. MARCO CLIMENT</t>
+          <t>V. SANTAMATILDE PERIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3052</v>
+        <v>-0.4321</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.286</v>
+        <v>0.0997</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5911999999999999</v>
+        <v>-0.5319</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5848</v>
+        <v>0.1119</v>
       </c>
       <c r="H5" t="n">
-        <v>1.519</v>
+        <v>-0.2982</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1038</v>
+        <v>0.41</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4153</v>
+        <v>0.4144</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5294</v>
+        <v>-0.2745</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.9446</v>
+        <v>0.6889</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1695</v>
+        <v>-0.3026</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0104</v>
+        <v>-0.0236</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1591</v>
+        <v>-0.2789</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3632</v>
+        <v>0.3895</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1158</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7526</v>
+        <v>0.3895</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0321</v>
+        <v>-0.0951</v>
       </c>
       <c r="T5" t="n">
-        <v>2.024</v>
+        <v>-0.3147</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9919</v>
+        <v>0.2196</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2211</v>
+        <v>-0.8384</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.8384</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. SANTAMATILDE PERIS</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3092</v>
+        <v>-0.6272</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001</v>
+        <v>-1.4553</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3093</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1119</v>
+        <v>1.0277</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2982</v>
+        <v>-0.9724</v>
       </c>
       <c r="I6" t="n">
-        <v>0.41</v>
+        <v>2.0001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4144</v>
+        <v>1.367</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2745</v>
+        <v>-0.6593</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6889</v>
+        <v>2.0263</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3026</v>
+        <v>-0.3393</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0236</v>
+        <v>-0.3131</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2789</v>
+        <v>-0.0262</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3895</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.921</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3895</v>
+        <v>1.7526</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0279</v>
+        <v>-0.207</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4144</v>
+        <v>0.0988</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4423</v>
+        <v>-0.3057</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8384</v>
+        <v>-0.2795</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8384</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MARTINEZ JURADO</t>
+          <t>F. MARCO CLIMENT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7164</v>
+        <v>-0.8213</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1307</v>
+        <v>-1.496</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4143</v>
+        <v>0.6747</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2311</v>
+        <v>-0.5848</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0643</v>
+        <v>1.519</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1669</v>
+        <v>-2.1038</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7179</v>
+        <v>-0.4153</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6774</v>
+        <v>1.5294</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>-1.9446</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5132</v>
+        <v>-0.1695</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3869</v>
+        <v>-0.0104</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1263</v>
+        <v>-0.1591</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9737</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1421</v>
+        <v>-3.1158</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1684</v>
+        <v>1.7526</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2473</v>
+        <v>-0.0944</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2935</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0462</v>
+        <v>-0.9084</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2211</v>
+        <v>1.2211</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. MORATA</t>
+          <t>D. MARTINEZ JURADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9154</v>
+        <v>-0.8817</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3399</v>
+        <v>-1.2682</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5754</v>
+        <v>0.3865</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2811</v>
+        <v>1.2311</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0605</v>
+        <v>1.0643</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2205</v>
+        <v>0.1669</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.7179</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.6774</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1139</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5077</v>
+        <v>0.5132</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6143999999999999</v>
+        <v>0.3869</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1067</v>
+        <v>0.1263</v>
       </c>
       <c r="P8" t="n">
         <v>-0.9737</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.921</v>
+        <v>-2.1421</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9474</v>
+        <v>1.1684</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9983</v>
+        <v>0.0819</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7923</v>
+        <v>0.156</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.794</v>
+        <v>-0.0741</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2211</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>E. MORATA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.468</v>
+        <v>-1.4492</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1013</v>
+        <v>-0.7903</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6333</v>
+        <v>-0.6589</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0277</v>
+        <v>0.2811</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9724</v>
+        <v>0.0605</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0001</v>
+        <v>0.2205</v>
       </c>
       <c r="J9" t="n">
-        <v>1.367</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6593</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>2.0263</v>
+        <v>0.1139</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3393</v>
+        <v>-0.5077</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3131</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0262</v>
+        <v>0.1067</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1684</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.921</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7526</v>
+        <v>1.9474</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0478</v>
+        <v>0.4645</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5473</v>
+        <v>1.3419</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2795</v>
+        <v>-1.2211</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2795</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1907</v>
+        <v>-1.945</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6834</v>
+        <v>-1.2986</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5073</v>
+        <v>-0.6464</v>
       </c>
       <c r="G10" t="n">
         <v>2.2758</v>
@@ -1234,13 +1234,13 @@
         <v>1.3632</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7139</v>
+        <v>-0.4682</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3433</v>
+        <v>0.0415</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3706</v>
+        <v>-0.5097</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2211</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0055</v>
+        <v>-2.3207</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9033</v>
+        <v>-2.5803</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1022</v>
+        <v>0.2596</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6492</v>
@@ -1312,13 +1312,13 @@
         <v>1.7526</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2521</v>
+        <v>-0.5674</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2261</v>
+        <v>0.0969</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.026</v>
+        <v>-0.6643</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6621</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3447</v>
+        <v>-2.5233</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9749</v>
+        <v>-2.1535</v>
       </c>
       <c r="F12" t="n">
         <v>-0.3697</v>
@@ -1390,10 +1390,10 @@
         <v>1.1684</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3105</v>
+        <v>-0.4891</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6617</v>
+        <v>0.1597</v>
       </c>
       <c r="U12" t="n">
         <v>-0.6488</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9162</v>
+        <v>-3.2485</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5153</v>
+        <v>-3.9311</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5991</v>
+        <v>0.6826</v>
       </c>
       <c r="G13" t="n">
         <v>-1.156</v>
@@ -1468,13 +1468,13 @@
         <v>1.1684</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9365</v>
+        <v>-0.2688</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3618</v>
+        <v>0.2224</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5747</v>
+        <v>-0.4912</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0447</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.2067</v>
+        <v>-10.6607</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.8698</v>
+        <v>-13.3241</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6632</v>
+        <v>2.6634</v>
       </c>
       <c r="G14" t="n">
         <v>0.2172999999999996</v>
@@ -1522,7 +1522,7 @@
         <v>2.3079</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7166000000000001</v>
+        <v>0.716600000000001</v>
       </c>
       <c r="L14" t="n">
         <v>1.5914</v>
@@ -1546,13 +1546,13 @@
         <v>14.6052</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.2301</v>
+        <v>-1.6844</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0015</v>
+        <v>2.5473</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.2316</v>
+        <v>-4.2318</v>
       </c>
       <c r="V14" t="n">
         <v>-4.3253</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7106</v>
+        <v>5.1423</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9104</v>
+        <v>2.4042</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8003</v>
+        <v>2.7381</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0355</v>
+        <v>1.9453</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8036</v>
+        <v>1.329</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2319</v>
+        <v>0.6163</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3472</v>
+        <v>1.9399</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6339</v>
+        <v>1.4368</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7134</v>
+        <v>0.503</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6883</v>
+        <v>0.0054</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1698</v>
+        <v>-0.1078</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5185</v>
+        <v>0.1132</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5842000000000001</v>
+        <v>1.3632</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9737</v>
+        <v>-1.1684</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5579</v>
+        <v>2.5316</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8698</v>
+        <v>0.6128</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9778</v>
+        <v>0.4116</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.108</v>
+        <v>0.2012</v>
       </c>
       <c r="V15" t="n">
         <v>1.2211</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5590000000000001</v>
+        <v>1.2211</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9578</v>
+        <v>5.0918</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5071</v>
+        <v>1.6146</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4507</v>
+        <v>3.4772</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9453</v>
+        <v>2.0355</v>
       </c>
       <c r="H16" t="n">
-        <v>1.329</v>
+        <v>0.8036</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6163</v>
+        <v>1.2319</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9399</v>
+        <v>1.3472</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4368</v>
+        <v>0.6339</v>
       </c>
       <c r="L16" t="n">
-        <v>0.503</v>
+        <v>0.7134</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0054</v>
+        <v>0.6883</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1078</v>
+        <v>0.1698</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1132</v>
+        <v>0.5185</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3632</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1684</v>
+        <v>-0.9737</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5316</v>
+        <v>1.5579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5717</v>
+        <v>1.251</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4854</v>
+        <v>0.6821</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0862</v>
+        <v>0.569</v>
       </c>
       <c r="V16" t="n">
         <v>1.2211</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2211</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9776</v>
+        <v>3.9967</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5089</v>
+        <v>2.2066</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4687</v>
+        <v>1.7901</v>
       </c>
       <c r="G17" t="n">
         <v>1.1444</v>
@@ -1780,13 +1780,13 @@
         <v>1.9474</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3616</v>
+        <v>0.6576</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6091</v>
+        <v>0.0886</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2475</v>
+        <v>0.569</v>
       </c>
       <c r="V17" t="n">
         <v>1.2211</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.9721</v>
+        <v>3.1444</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5061</v>
+        <v>1.4065</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4659</v>
+        <v>1.738</v>
       </c>
       <c r="G18" t="n">
         <v>2.0522</v>
@@ -1858,13 +1858,13 @@
         <v>1.5579</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3678</v>
+        <v>0.5401</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4882</v>
+        <v>0.3886</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1204</v>
+        <v>0.1516</v>
       </c>
       <c r="V18" t="n">
         <v>0.9416</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7046</v>
+        <v>1.6768</v>
       </c>
       <c r="E19" t="n">
-        <v>0.864</v>
+        <v>0.4653</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8406</v>
+        <v>1.2115</v>
       </c>
       <c r="G19" t="n">
         <v>0.8113</v>
@@ -1936,13 +1936,13 @@
         <v>1.3632</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5038</v>
+        <v>0.476</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8436</v>
+        <v>0.4449</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3397</v>
+        <v>0.0311</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2937</v>
+        <v>1.2057</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2679</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0258</v>
+        <v>1.1371</v>
       </c>
       <c r="G20" t="n">
         <v>0.0876</v>
@@ -2014,13 +2014,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1545</v>
+        <v>0.0665</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4172</v>
+        <v>0.2178</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2627</v>
+        <v>-0.1514</v>
       </c>
       <c r="V20" t="n">
         <v>0.6621</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6079</v>
+        <v>1.0269</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6079</v>
+        <v>-0.3303</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1.3572</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6079</v>
+        <v>-0.8551</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-1.0935</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6079</v>
+        <v>0.2384</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6079</v>
+        <v>-0.3697</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-0.9133</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6079</v>
+        <v>0.5436</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>-0.4854</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.1802</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.3052</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.5579</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.4915</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.2068</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.2847</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CANAS</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4949</v>
+        <v>0.6079</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.625</v>
+        <v>0.6079</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1198</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.425</v>
+        <v>0.6079</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2581</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1669</v>
+        <v>0.6079</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.6079</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6081</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0405</v>
+        <v>0.6079</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2236</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1263</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3895</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3632</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0401</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2999</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. GONZALEZ  LONGARELA</t>
+          <t>D. FERNANDEZ CANAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3079</v>
+        <v>0.5551</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3079</v>
+        <v>-0.4256</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.9807</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3079</v>
+        <v>0.425</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3079</v>
+        <v>0.2581</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.1669</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3079</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3079</v>
+        <v>0.6081</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>-0.2236</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>0.1263</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.3895</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.3632</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.0201</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-0.1006</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>0.1207</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>D. GONZALEZ  LONGARELA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0704</v>
+        <v>0.3079</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.729</v>
+        <v>0.3079</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6587</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8551</v>
+        <v>0.3079</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0935</v>
+        <v>0.3079</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2384</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3697</v>
+        <v>0.3079</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9133</v>
+        <v>0.3079</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5436</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4854</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1802</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3052</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3895</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5579</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6058</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.192</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4139</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>N. MAIGA</t>
+          <t>F. GOMEZ DE ENTERRIA LOPEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.166</v>
+        <v>-0.7953</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.4974</v>
+        <v>-1.3135</v>
       </c>
       <c r="F25" t="n">
-        <v>3.3314</v>
+        <v>0.5182</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.3067</v>
+        <v>-1.6595</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.2917</v>
+        <v>-1.0761</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.015</v>
+        <v>-0.5835</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.2806</v>
+        <v>-1.2175</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.5707</v>
+        <v>-1.1853</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.7098</v>
+        <v>-0.0322</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0261</v>
+        <v>-0.442</v>
       </c>
       <c r="N25" t="n">
-        <v>0.279</v>
+        <v>0.1093</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3052</v>
+        <v>-0.5513</v>
       </c>
       <c r="P25" t="n">
-        <v>1.3632</v>
+        <v>0.9737</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1684</v>
+        <v>-0.1947</v>
       </c>
       <c r="R25" t="n">
-        <v>2.5316</v>
+        <v>1.1684</v>
       </c>
       <c r="S25" t="n">
-        <v>1.7775</v>
+        <v>0.17</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9516</v>
+        <v>0.0988</v>
       </c>
       <c r="U25" t="n">
-        <v>0.826</v>
+        <v>0.0713</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>F. GOMEZ DE ENTERRIA LOPEZ</t>
+          <t>N. MAIGA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.2434</v>
+        <v>-1.2906</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.7122</v>
+        <v>-4.5971</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4688</v>
+        <v>3.3065</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.6595</v>
+        <v>-4.3067</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.0761</v>
+        <v>-2.2917</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5835</v>
+        <v>-2.015</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.2175</v>
+        <v>-4.2806</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.1853</v>
+        <v>-2.5707</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.0322</v>
+        <v>-1.7098</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.442</v>
+        <v>-0.0261</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1093</v>
+        <v>0.279</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.5513</v>
+        <v>-0.3052</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9737</v>
+        <v>1.3632</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.1947</v>
+        <v>-1.1684</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1684</v>
+        <v>2.5316</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2781</v>
+        <v>1.653</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2999</v>
+        <v>0.8519</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0219</v>
+        <v>0.8011</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.8178</v>
+        <v>-2.3934</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8904</v>
+        <v>-1.7875</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.9274</v>
+        <v>-0.6059</v>
       </c>
       <c r="G27" t="n">
         <v>-1.1381</v>
@@ -2560,13 +2560,13 @@
         <v>1.7526</v>
       </c>
       <c r="S27" t="n">
-        <v>1.1188</v>
+        <v>0.5431</v>
       </c>
       <c r="T27" t="n">
-        <v>1.5791</v>
+        <v>0.6821</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.4604</v>
+        <v>-0.1389</v>
       </c>
       <c r="V27" t="n">
         <v>-1.6037</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.5229</v>
+        <v>-2.7471</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.6895</v>
+        <v>-3.2908</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1666</v>
+        <v>0.5437</v>
       </c>
       <c r="G28" t="n">
         <v>-1.675</v>
@@ -2638,13 +2638,13 @@
         <v>1.5579</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.7047</v>
+        <v>0.0711</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.1393</v>
+        <v>0.2594</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.5654</v>
+        <v>-0.1883</v>
       </c>
       <c r="V28" t="n">
         <v>-0.5590000000000001</v>
@@ -2671,22 +2671,22 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>12.2066</v>
+        <v>15.5291</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.663299999999999</v>
+        <v>-2.663199999999998</v>
       </c>
       <c r="F29" t="n">
-        <v>14.8699</v>
+        <v>18.19240000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2172999999999989</v>
+        <v>-0.2172999999999985</v>
       </c>
       <c r="H29" t="n">
-        <v>1.144300000000001</v>
+        <v>1.1443</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.361700000000001</v>
+        <v>-1.3617</v>
       </c>
       <c r="J29" t="n">
         <v>2.0907</v>
@@ -2695,13 +2695,13 @@
         <v>1.8611</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2295</v>
+        <v>0.2295000000000005</v>
       </c>
       <c r="M29" t="n">
         <v>-2.3078</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.7164999999999998</v>
+        <v>-0.7164999999999999</v>
       </c>
       <c r="O29" t="n">
         <v>-1.5915</v>
@@ -2716,13 +2716,13 @@
         <v>19.4738</v>
       </c>
       <c r="S29" t="n">
-        <v>3.2302</v>
+        <v>6.5528</v>
       </c>
       <c r="T29" t="n">
-        <v>4.2319</v>
+        <v>4.232</v>
       </c>
       <c r="U29" t="n">
-        <v>-1.0015</v>
+        <v>2.3211</v>
       </c>
       <c r="V29" t="n">
         <v>4.325300000000001</v>
